--- a/verification-2026-05-21.xlsx
+++ b/verification-2026-05-21.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>98dc1d22-13a3-49f3-8e33-ad1546784a08</t>
+          <t>&lt;your-admin-user-id&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>{"id":"eaacabf3-82f1-49b5-bd79-eab7a88e5446","date":"1990-01-01","notes":"=1+1","org_id":"00000000-0000-0000-0000-000000000001","user_id":"98dc1d22-13a3-49f3-8e33-ad1546784a08","er_visits":0,"created_at":"2026-05-21T06:00:56.637974+00:00","avg_wait_time_mins":0,"icu_beds_available":0,"patient_admissions":0,"patient_discharges":0,"bed_occupancy_percent":0}</t>
+          <t>{"id":"eaacabf3-82f1-49b5-bd79-eab7a88e5446","date":"1990-01-01","notes":"=1+1","org_id":"00000000-0000-0000-0000-000000000001","user_id":"&lt;your-admin-user-id&gt;","er_visits":0,"created_at":"2026-05-21T06:00:56.637974+00:00","avg_wait_time_mins":0,"icu_beds_available":0,"patient_admissions":0,"patient_discharges":0,"bed_occupancy_percent":0}</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>98dc1d22-13a3-49f3-8e33-ad1546784a08</t>
+          <t>&lt;your-admin-user-id&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"id":"eaacabf3-82f1-49b5-bd79-eab7a88e5446","date":"1990-01-01","notes":"=1+1","org_id":"00000000-0000-0000-0000-000000000001","user_id":"98dc1d22-13a3-49f3-8e33-ad1546784a08","er_visits":0,"created_at":"2026-05-21T06:00:56.637974+00:00","avg_wait_time_mins":0,"icu_beds_available":0,"patient_admissions":0,"patient_discharges":0,"bed_occupancy_percent":0}</t>
+          <t>{"id":"eaacabf3-82f1-49b5-bd79-eab7a88e5446","date":"1990-01-01","notes":"=1+1","org_id":"00000000-0000-0000-0000-000000000001","user_id":"&lt;your-admin-user-id&gt;","er_visits":0,"created_at":"2026-05-21T06:00:56.637974+00:00","avg_wait_time_mins":0,"icu_beds_available":0,"patient_admissions":0,"patient_discharges":0,"bed_occupancy_percent":0}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -968,6 +968,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
